--- a/output/laminas_comunales/comunal_i_ingr_a_2022_coquimbo.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_a_2022_coquimbo.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -381,11 +381,6 @@
           <t>delta_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>is_emph</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -396,9 +391,6 @@
       <c r="B2">
         <v>1187623.75</v>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -409,9 +401,6 @@
       <c r="B3">
         <v>1106701.25</v>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -422,9 +411,6 @@
       <c r="B4">
         <v>1045537.81</v>
       </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -435,9 +421,6 @@
       <c r="B5">
         <v>1029611.69</v>
       </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -448,9 +431,6 @@
       <c r="B6">
         <v>1028576.44</v>
       </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -461,9 +441,6 @@
       <c r="B7">
         <v>928347.62</v>
       </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -474,9 +451,6 @@
       <c r="B8">
         <v>923633.38</v>
       </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -487,9 +461,6 @@
       <c r="B9">
         <v>920945.38</v>
       </c>
-      <c r="F9" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -500,9 +471,6 @@
       <c r="B10">
         <v>891493.1899999999</v>
       </c>
-      <c r="F10" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -513,9 +481,6 @@
       <c r="B11">
         <v>887502</v>
       </c>
-      <c r="F11" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -526,9 +491,6 @@
       <c r="B12">
         <v>871820.12</v>
       </c>
-      <c r="F12" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -539,9 +501,6 @@
       <c r="B13">
         <v>865779.25</v>
       </c>
-      <c r="F13" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -552,9 +511,6 @@
       <c r="B14">
         <v>833374.4399999999</v>
       </c>
-      <c r="F14" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -565,9 +521,6 @@
       <c r="B15">
         <v>785699.38</v>
       </c>
-      <c r="F15" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -577,9 +530,6 @@
       </c>
       <c r="B16">
         <v>784520.8100000001</v>
-      </c>
-      <c r="F16" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_i_ingr_a_2022_coquimbo.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_a_2022_coquimbo.xlsx
@@ -391,6 +391,15 @@
       <c r="B2">
         <v>1187623.75</v>
       </c>
+      <c r="C2">
+        <v>1060258.62</v>
+      </c>
+      <c r="D2">
+        <v>127365.1299999999</v>
+      </c>
+      <c r="E2">
+        <v>12.01264744256452</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -401,6 +410,15 @@
       <c r="B3">
         <v>1106701.25</v>
       </c>
+      <c r="C3">
+        <v>926020.6899999999</v>
+      </c>
+      <c r="D3">
+        <v>180680.5600000001</v>
+      </c>
+      <c r="E3">
+        <v>19.5115035712647</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -411,115 +429,223 @@
       <c r="B4">
         <v>1045537.81</v>
       </c>
+      <c r="C4">
+        <v>928331.8100000001</v>
+      </c>
+      <c r="D4">
+        <v>117206</v>
+      </c>
+      <c r="E4">
+        <v>12.62544262056473</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Salamanca</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B5">
-        <v>1029611.69</v>
+        <v>1037000.75</v>
+      </c>
+      <c r="C5">
+        <v>917934</v>
+      </c>
+      <c r="D5">
+        <v>119066.75</v>
+      </c>
+      <c r="E5">
+        <v>12.97116677233876</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Illapel</t>
+          <t>Salamanca</t>
         </is>
       </c>
       <c r="B6">
-        <v>1028576.44</v>
+        <v>1029611.69</v>
+      </c>
+      <c r="C6">
+        <v>914388.5</v>
+      </c>
+      <c r="D6">
+        <v>115223.1899999999</v>
+      </c>
+      <c r="E6">
+        <v>12.60111976473894</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Punitaqui</t>
+          <t>Illapel</t>
         </is>
       </c>
       <c r="B7">
-        <v>928347.62</v>
+        <v>1028576.44</v>
+      </c>
+      <c r="C7">
+        <v>916712.12</v>
+      </c>
+      <c r="D7">
+        <v>111864.3199999999</v>
+      </c>
+      <c r="E7">
+        <v>12.20277528347722</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Río Hurtado</t>
+          <t>Punitaqui</t>
         </is>
       </c>
       <c r="B8">
-        <v>923633.38</v>
+        <v>928347.62</v>
+      </c>
+      <c r="C8">
+        <v>785889.75</v>
+      </c>
+      <c r="D8">
+        <v>142457.87</v>
+      </c>
+      <c r="E8">
+        <v>18.12695355805314</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Los Vilos</t>
+          <t>Río Hurtado</t>
         </is>
       </c>
       <c r="B9">
-        <v>920945.38</v>
+        <v>923633.38</v>
+      </c>
+      <c r="C9">
+        <v>758336.9399999999</v>
+      </c>
+      <c r="D9">
+        <v>165296.4400000001</v>
+      </c>
+      <c r="E9">
+        <v>21.79722907867314</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Canela</t>
+          <t>Los Vilos</t>
         </is>
       </c>
       <c r="B10">
-        <v>891493.1899999999</v>
+        <v>920945.38</v>
+      </c>
+      <c r="C10">
+        <v>823746</v>
+      </c>
+      <c r="D10">
+        <v>97199.38</v>
+      </c>
+      <c r="E10">
+        <v>11.7996785416864</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ovalle</t>
+          <t>Canela</t>
         </is>
       </c>
       <c r="B11">
-        <v>887502</v>
+        <v>891493.1899999999</v>
+      </c>
+      <c r="C11">
+        <v>769717</v>
+      </c>
+      <c r="D11">
+        <v>121776.1899999999</v>
+      </c>
+      <c r="E11">
+        <v>15.82090430638792</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>La Higuera</t>
+          <t>Ovalle</t>
         </is>
       </c>
       <c r="B12">
-        <v>871820.12</v>
+        <v>887502</v>
+      </c>
+      <c r="C12">
+        <v>784629.5600000001</v>
+      </c>
+      <c r="D12">
+        <v>102872.4399999999</v>
+      </c>
+      <c r="E12">
+        <v>13.11095646205325</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Combarbalá</t>
+          <t>La Higuera</t>
         </is>
       </c>
       <c r="B13">
-        <v>865779.25</v>
+        <v>871820.12</v>
+      </c>
+      <c r="C13">
+        <v>788636.4399999999</v>
+      </c>
+      <c r="D13">
+        <v>83183.68000000005</v>
+      </c>
+      <c r="E13">
+        <v>10.54778549162654</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Vicuña</t>
+          <t>Combarbalá</t>
         </is>
       </c>
       <c r="B14">
-        <v>833374.4399999999</v>
+        <v>865779.25</v>
+      </c>
+      <c r="C14">
+        <v>727910</v>
+      </c>
+      <c r="D14">
+        <v>137869.25</v>
+      </c>
+      <c r="E14">
+        <v>18.94042532730695</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Paiguano</t>
+          <t>Vicuña</t>
         </is>
       </c>
       <c r="B15">
-        <v>785699.38</v>
+        <v>833374.4399999999</v>
+      </c>
+      <c r="C15">
+        <v>726673</v>
+      </c>
+      <c r="D15">
+        <v>106701.4399999999</v>
+      </c>
+      <c r="E15">
+        <v>14.68355642771919</v>
       </c>
     </row>
     <row r="16">
@@ -530,6 +656,15 @@
       </c>
       <c r="B16">
         <v>784520.8100000001</v>
+      </c>
+      <c r="C16">
+        <v>683556.88</v>
+      </c>
+      <c r="D16">
+        <v>100963.9300000001</v>
+      </c>
+      <c r="E16">
+        <v>14.77037726545889</v>
       </c>
     </row>
   </sheetData>
@@ -539,7 +674,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -657,50 +792,40 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Paiguano</t>
+          <t>Punitaqui</t>
         </is>
       </c>
       <c r="B12">
-        <v>785699.38</v>
+        <v>928347.62</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Punitaqui</t>
+          <t>Río Hurtado</t>
         </is>
       </c>
       <c r="B13">
-        <v>928347.62</v>
+        <v>923633.38</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Río Hurtado</t>
+          <t>Salamanca</t>
         </is>
       </c>
       <c r="B14">
-        <v>923633.38</v>
+        <v>1029611.69</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Salamanca</t>
+          <t>Vicuña</t>
         </is>
       </c>
       <c r="B15">
-        <v>1029611.69</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Vicuña</t>
-        </is>
-      </c>
-      <c r="B16">
         <v>833374.4399999999</v>
       </c>
     </row>

--- a/output/laminas_comunales/comunal_i_ingr_a_2022_coquimbo.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_a_2022_coquimbo.xlsx
@@ -674,7 +674,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -683,11 +683,6 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -695,138 +690,103 @@
           <t>Andacollo</t>
         </is>
       </c>
-      <c r="B2">
-        <v>1106701.25</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Canela</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>891493.1899999999</v>
+          <t>Los Vilos</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Combarbalá</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>865779.25</v>
+          <t>Canela</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>1045537.81</v>
+          <t>Ovalle</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Illapel</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>1028576.44</v>
+          <t>Coquimbo</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>La Higuera</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>871820.12</v>
+          <t>La Serena</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>La Serena</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>1187623.75</v>
+          <t>Combarbalá</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Los Vilos</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>920945.38</v>
+          <t>Punitaqui</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Monte Patria</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>784520.8100000001</v>
+          <t>Paihuano</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ovalle</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>887502</v>
+          <t>Illapel</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Punitaqui</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>928347.62</v>
+          <t>La Higuera</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Río Hurtado</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>923633.38</v>
+          <t>Monte Patria</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Salamanca</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>1029611.69</v>
+          <t>Río Hurtado</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>Vicuña</t>
         </is>
-      </c>
-      <c r="B15">
-        <v>833374.4399999999</v>
       </c>
     </row>
   </sheetData>
